--- a/results/job_matches_2026-09-13.xlsx
+++ b/results/job_matches_2026-09-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>AWS Data Engineer (Databricks, AWS, Python)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5ac038b52e4c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=595b0051a2bcc4f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Databricks, AWS, Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Databricks</t>
+          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595b0051a2bcc4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Remote Opportunity!</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, GCP, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
+          <t>https://www.indeed.com/viewjob?jk=8e29b703157f7cf6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote Opportunity!</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, GCP, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e29b703157f7cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>API Gateway, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=42f48af529b6933f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Service Delivery Center, Workflow Platform Backend Engineer - Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,24 +731,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f48af529b6933f</t>
+          <t>https://www.indeed.com/viewjob?jk=83a6b09a8c7e1119</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Workflow Platform Backend Engineer - Senior</t>
+          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a6b09a8c7e1119</t>
+          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineer</t>
+          <t>Service Delivery Center - Apigee Migration Engineer - Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156843bab1a1eb41</t>
+          <t>https://www.indeed.com/viewjob?jk=d02fbb8686e98a85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Kavant Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, ETL, Talend, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
+          <t>https://www.indeed.com/viewjob?jk=84f280b9c5186dbd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Data Engineer, Foundations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>State Teachers' Retirement System</t>
+          <t>Superhuman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dbecd28bfb842</t>
+          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Service Delivery Center - Apigee Migration Engineer - Senior</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Princeton University</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02fbb8686e98a85</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kavant Solutions</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, ETL, Talend, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f280b9c5186dbd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer, Foundations</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Superhuman</t>
+          <t>ZBD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Oracle Database Admin - SQL/ETL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2d3fa65c104128</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b24eb9546bc51</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Senior Software Engineer, Quality &amp; Automation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4badb7c2f63bb4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Commercial Data</t>
+          <t>Enterprise Solution Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,357 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b2b9beddde03a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ZBD</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Engineer - Finance AI Solutions</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Brooklyn Park, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84bfe83ebefec716</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Quality &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Crum &amp; Forster</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Glastonbury, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Softek International Inc</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, IAM, RDS, Databricks, Unity Catalog, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4945bb4012ef1aca</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>IT System Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Nelnet</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=effbbb7a20b14c79</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Python, Databricks</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2395a3423532a7f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Software Engineer III-ETL/PySpark</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=691f4a76da481428</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, ML Ops</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>PathAI</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, MLOps, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efb2a43efc0c3365</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect, AI Health Cloud</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>BrightSpring Health Services</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>STAR Autism Support</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Beaverton, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, AKS, pytest, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=489e0afc743493db</t>
         </is>
       </c>
     </row>
